--- a/frontend/public/metadata_template.xlsx
+++ b/frontend/public/metadata_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cells" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cells" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -143,7 +143,8 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Required. Must equal the number in each cell's cycling filename.</t>
+        <t>The cycling data file you upload must contain this ID No in its filename.
+Examples: 12_cycling.xlsx / CEL-12_data.csv</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
@@ -746,7 +747,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/frontend/public/metadata_template.xlsx
+++ b/frontend/public/metadata_template.xlsx
@@ -143,8 +143,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>The cycling data file you upload must contain this ID No in its filename.
-Examples: 12_cycling.xlsx / CEL-12_data.csv</t>
+        <t>Required. Must equal the number in each cell's cycling filename.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
@@ -155,6 +154,11 @@
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Matched by value, so 1 and 1.0 are the same condition.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Columns beyond the standard set are preserved as-is, shown on the cell card, and selectable as a hierarchy filter — add any you need.</t>
       </text>
     </comment>
   </commentList>
@@ -450,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -474,6 +478,9 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
     <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,6 +589,21 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Cathode supplier</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Electrolyte supplier</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Testing procedure</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -667,6 +689,21 @@
           <t>first replicate</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Canrud</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Canrud</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>rate performance</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -745,6 +782,22 @@
       <c r="T3" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Canrud</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Canrud</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>formation</t>
         </is>
       </c>
     </row>
